--- a/assets/Ra_Soat_Thiet_Bi_CNTT.xlsx
+++ b/assets/Ra_Soat_Thiet_Bi_CNTT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2023\CCDC, TB, PTVC\CCDC,TB\PM QLTB\device-inventory-web\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F50025-3483-49A8-8029-9CAA77506273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E6DE9C8-48BF-46F4-BF0C-32D426C1801C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="4725" windowWidth="21600" windowHeight="11295" tabRatio="827" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="827" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Hidden" sheetId="1" state="hidden" r:id="rId1"/>
@@ -36,6 +36,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'8. Thiết Bị Khác'!$A$4:$Y$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1243,6 +1244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1484,6 +1486,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:Y54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3066,6 +3069,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:Y54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4664,6 +4668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:B44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4863,6 +4868,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -5682,6 +5688,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AD54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -7552,6 +7559,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:W54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -9037,6 +9045,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:W54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10522,6 +10531,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:AA54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -12229,6 +12239,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:W54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -13714,6 +13725,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
